--- a/Dati/Estraz_plasma_PB8.xlsx
+++ b/Dati/Estraz_plasma_PB8.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camillo\GitHub\DoE_en\Shiny\Dati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RSTUDIOAPPLICATIVI\DoE\Dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D67931-EAEA-49F4-9B39-5EDF04C67848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEF9C02-0B38-4EB3-B239-85E9D017EC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{65F41629-7783-4282-AE5B-460B39DDAF8C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{65F41629-7783-4282-AE5B-460B39DDAF8C}"/>
   </bookViews>
   <sheets>
     <sheet name="PB1 Estraz plasma" sheetId="1" r:id="rId1"/>
+    <sheet name="Costruzione" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>SI</t>
   </si>
@@ -73,9 +74,6 @@
     <t>Tempo misc</t>
   </si>
   <si>
-    <t>Vol sovente</t>
-  </si>
-  <si>
     <t>Vol plasma</t>
   </si>
   <si>
@@ -101,14 +99,70 @@
   </si>
   <si>
     <t>x1</t>
+  </si>
+  <si>
+    <t>Fattore</t>
+  </si>
+  <si>
+    <t>Livello -1</t>
+  </si>
+  <si>
+    <t>Livello +1</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Vol plasma (µL)</t>
+  </si>
+  <si>
+    <t>Vol solvente (µL)</t>
+  </si>
+  <si>
+    <t>Vol solvente</t>
+  </si>
+  <si>
+    <t>3x</t>
+  </si>
+  <si>
+    <t>7x</t>
+  </si>
+  <si>
+    <t>Il volume del solvente è calcolato rispetto al volume del plasma: 3 volte o 7 volte.</t>
+  </si>
+  <si>
+    <t>Tempo misc (sec)</t>
+  </si>
+  <si>
+    <t>temp centr (min)</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Tempo di miscelazione plasma-solvente deproteinizzante</t>
+  </si>
+  <si>
+    <t>tempo di centrifugazione della miscela dopo deproteinizzazione</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -261,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -269,42 +323,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -320,9 +383,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -360,7 +423,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -466,7 +529,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -608,7 +671,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -617,435 +680,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC666E6-88F0-462F-8B39-5123F023826F}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="8.88671875" style="1"/>
+    <col min="1" max="8" width="8.85546875" style="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>-1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="3">
         <v>-1</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="1">
         <v>200</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="1">
         <v>1400</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="1">
         <v>20</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="7">
         <v>31795</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>-1</v>
       </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>-1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
         <v>-1</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>200</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="1">
         <v>1400</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="1">
         <v>60</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="1">
         <v>4</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="7">
         <v>33313</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>-1</v>
       </c>
-      <c r="B4" s="3">
-        <v>-1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="B4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="3">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="1">
         <v>50</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="1">
         <v>350</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="1">
         <v>60</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="1">
         <v>25</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="s">
+      <c r="M4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="7">
         <v>32264</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="B5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
         <v>-1</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="1">
         <v>50</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="1">
         <v>150</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="1">
         <v>60</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="1">
         <v>25</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="7">
         <v>31559</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>-1</v>
       </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>-1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="1">
         <v>200</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="1">
         <v>600</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="1">
         <v>20</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="1">
         <v>25</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <v>35150</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>1</v>
       </c>
-      <c r="B7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="B7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="1">
         <v>50</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="1">
         <v>350</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="1">
         <v>20</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="7">
         <v>21201</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>-1</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="1">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="1">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="1">
         <v>60</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="1">
         <v>4</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4" t="s">
+      <c r="M8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <v>32344</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>-1</v>
-      </c>
-      <c r="B9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>-1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>50</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>150</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>20</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>4</v>
       </c>
-      <c r="M9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7" t="s">
+      <c r="M9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="8">
         <v>21087</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1057,4 +1124,120 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9911D4E0-FE74-47E4-9104-06A4F7432FD1}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="3" width="11.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="75.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>